--- a/examples/lau_phd_context.xlsx
+++ b/examples/lau_phd_context.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/unafarrell/Dropbox/Database/Templates/git/sgp-context-template/examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CFDB1B4-E081-E249-B4BF-559F5393A61A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFEA91BA-D7B1-2D4A-B6F0-73317D528307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3220" yWindow="620" windowWidth="42720" windowHeight="18640" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3220" yWindow="620" windowWidth="42720" windowHeight="18640" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata + Guide" sheetId="8" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3191" uniqueCount="838">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3193" uniqueCount="840">
   <si>
     <t>lith_comp</t>
   </si>
@@ -2789,6 +2789,12 @@
   </si>
   <si>
     <t>U isotopes and associated major and trace elements (in the same table)</t>
+  </si>
+  <si>
+    <t>Kimberly Lau</t>
+  </si>
+  <si>
+    <t>New version of this context sheet, to serve as an example.</t>
   </si>
 </sst>
 </file>
@@ -3193,7 +3199,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3327,6 +3333,7 @@
     </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="202">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
@@ -3965,15 +3972,24 @@
       <c r="A10" s="43" t="s">
         <v>510</v>
       </c>
+      <c r="B10" t="s">
+        <v>838</v>
+      </c>
     </row>
     <row r="11" spans="1:4" ht="19" x14ac:dyDescent="0.25">
       <c r="A11" s="43" t="s">
         <v>508</v>
       </c>
+      <c r="B11" s="65">
+        <v>44429</v>
+      </c>
     </row>
     <row r="12" spans="1:4" ht="19" x14ac:dyDescent="0.25">
       <c r="A12" s="43" t="s">
         <v>506</v>
+      </c>
+      <c r="B12" t="s">
+        <v>839</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="19" x14ac:dyDescent="0.25">
